--- a/03_Outputs/Bioenergetica_Norte/09_Salud/salud.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/09_Salud/salud.xlsx
@@ -11,6 +11,10 @@
     <sheet name="suicidios" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="aseguramiento_sgsss" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="mortalidad_infantil" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="_fig_01" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="_fig_02" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="_fig_03" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="_fig_04" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -805,7 +809,7 @@
         </is>
       </c>
       <c r="E15" s="5">
-        <v>0.122388124566012</v>
+        <v>0.117075551861405</v>
       </c>
     </row>
     <row r="16">
@@ -830,7 +834,7 @@
         </is>
       </c>
       <c r="E16" s="5">
-        <v>0.133154373496339</v>
+        <v>0.135131052465182</v>
       </c>
     </row>
     <row r="17">
@@ -855,7 +859,7 @@
         </is>
       </c>
       <c r="E17" s="5">
-        <v>0.104839029927317</v>
+        <v>0.1127786401623</v>
       </c>
     </row>
   </sheetData>
@@ -2823,7 +2827,7 @@
         <v>2020</v>
       </c>
       <c r="F15" s="29">
-        <v>8.16404529651678</v>
+        <v>8.53658536585366</v>
       </c>
     </row>
     <row r="16">
@@ -2851,7 +2855,7 @@
         <v>2020</v>
       </c>
       <c r="F16" s="29">
-        <v>7.04945276732133</v>
+        <v>6.6510172143975</v>
       </c>
     </row>
     <row r="17">
@@ -2879,7 +2883,7 @@
         <v>2020</v>
       </c>
       <c r="F17" s="29">
-        <v>8.46205433299409</v>
+        <v>7.73163562403355</v>
       </c>
     </row>
     <row r="18">
@@ -3245,7 +3249,7 @@
         <v>2021</v>
       </c>
       <c r="F31" s="29">
-        <v>11.6653370046335</v>
+        <v>15.0724637681159</v>
       </c>
     </row>
     <row r="32">
@@ -3273,7 +3277,7 @@
         <v>2021</v>
       </c>
       <c r="F32" s="29">
-        <v>9.38669976216444</v>
+        <v>10.916179337232</v>
       </c>
     </row>
     <row r="33">
@@ -3301,7 +3305,7 @@
         <v>2021</v>
       </c>
       <c r="F33" s="29">
-        <v>9.34976953784637</v>
+        <v>9.4518227498541</v>
       </c>
     </row>
     <row r="34">
@@ -3667,7 +3671,7 @@
         <v>2022</v>
       </c>
       <c r="F47" s="29">
-        <v>10.9429106546413</v>
+        <v>8.42865743527995</v>
       </c>
     </row>
     <row r="48">
@@ -3695,7 +3699,7 @@
         <v>2022</v>
       </c>
       <c r="F48" s="29">
-        <v>10.3032441385525</v>
+        <v>9.43009430094301</v>
       </c>
     </row>
     <row r="49">
@@ -3723,7 +3727,7 @@
         <v>2022</v>
       </c>
       <c r="F49" s="29">
-        <v>11.4029851073361</v>
+        <v>8.91172153491298</v>
       </c>
     </row>
     <row r="50">
@@ -4089,7 +4093,7 @@
         <v>2023</v>
       </c>
       <c r="F63" s="29">
-        <v>8.07838214760074</v>
+        <v>7.58150113722517</v>
       </c>
     </row>
     <row r="64">
@@ -4117,7 +4121,7 @@
         <v>2023</v>
       </c>
       <c r="F64" s="29">
-        <v>10.7022989966863</v>
+        <v>10.5263157894737</v>
       </c>
     </row>
     <row r="65">
@@ -4145,7 +4149,7 @@
         <v>2023</v>
       </c>
       <c r="F65" s="29">
-        <v>9.67146327493365</v>
+        <v>7.81130860599488</v>
       </c>
     </row>
     <row r="66">
@@ -4511,7 +4515,7 @@
         <v>2024</v>
       </c>
       <c r="F79" s="29">
-        <v>4.53660866936795</v>
+        <v>6.05012964563526</v>
       </c>
     </row>
     <row r="80">
@@ -4539,7 +4543,7 @@
         <v>2024</v>
       </c>
       <c r="F80" s="29">
-        <v>7.48288416411937</v>
+        <v>9.0702947845805</v>
       </c>
     </row>
     <row r="81">
@@ -4567,7 +4571,860 @@
         <v>2024</v>
       </c>
       <c r="F81" s="29">
-        <v>11.657876708496</v>
+        <v>8.64464932625405</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="4" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>prop_subsidiado</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>prop_contributivo</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>prop_especial</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.870137763371151</v>
+      </c>
+      <c r="C2">
+        <v>0.108286061588331</v>
+      </c>
+      <c r="D2">
+        <v>0.0215761750405186</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.891241799976982</v>
+      </c>
+      <c r="C3">
+        <v>0.0872942801242951</v>
+      </c>
+      <c r="D3">
+        <v>0.0214639198987225</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.860095389507154</v>
+      </c>
+      <c r="C4">
+        <v>0.102702702702703</v>
+      </c>
+      <c r="D4">
+        <v>0.0372019077901431</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.907524411257898</v>
+      </c>
+      <c r="C5">
+        <v>0.0690695002871913</v>
+      </c>
+      <c r="D5">
+        <v>0.023406088454911</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.554927587424938</v>
+      </c>
+      <c r="C6">
+        <v>0.392440833627693</v>
+      </c>
+      <c r="D6">
+        <v>0.0526315789473684</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.661618347035915</v>
+      </c>
+      <c r="C7">
+        <v>0.289629309101399</v>
+      </c>
+      <c r="D7">
+        <v>0.0487523438626857</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.763741754947032</v>
+      </c>
+      <c r="C8">
+        <v>0.211273236058365</v>
+      </c>
+      <c r="D8">
+        <v>0.0249850089946032</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.834207708779443</v>
+      </c>
+      <c r="C9">
+        <v>0.130728051391863</v>
+      </c>
+      <c r="D9">
+        <v>0.0350642398286938</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.733866666666667</v>
+      </c>
+      <c r="C10">
+        <v>0.236622222222222</v>
+      </c>
+      <c r="D10">
+        <v>0.0295111111111111</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.622869318181818</v>
+      </c>
+      <c r="C11">
+        <v>0.337713068181818</v>
+      </c>
+      <c r="D11">
+        <v>0.0394176136363636</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.809781432590348</v>
+      </c>
+      <c r="C12">
+        <v>0.161004111664142</v>
+      </c>
+      <c r="D12">
+        <v>0.0292144557455096</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.897715289982425</v>
+      </c>
+      <c r="C13">
+        <v>0.0760632688927944</v>
+      </c>
+      <c r="D13">
+        <v>0.0262214411247803</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.589440850277264</v>
+      </c>
+      <c r="C14">
+        <v>0.376894639556377</v>
+      </c>
+      <c r="D14">
+        <v>0.0336645101663586</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>bajo_peso</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.152941176470588</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.110552763819095</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.107692307692308</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.155172413793103</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.131578947368421</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.0555555555555556</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.0886075949367088</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.0384615384615385</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.269230769230769</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.0909090909090909</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.137254901960784</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.116071428571429</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="4" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>dengue</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>leishmaniasis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>25.6981836380206</v>
+      </c>
+      <c r="C3">
+        <v>826.95012209567</v>
+      </c>
+      <c r="D3">
+        <v>914.388344122628</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>11.9182711814397</v>
+      </c>
+      <c r="C4">
+        <v>6.31552355690287</v>
+      </c>
+      <c r="D4">
+        <v>113.000299069206</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>315.787889970579</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>15.7316444273443</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>7.02481756092709</v>
+      </c>
+      <c r="C9">
+        <v>36.2411400538298</v>
+      </c>
+      <c r="D9">
+        <v>139.159868316988</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>8.61994655633135</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>6.37958532695375</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>39.1220516137676</v>
+      </c>
+      <c r="C13">
+        <v>195.436461284722</v>
+      </c>
+      <c r="D13">
+        <v>1167.87377976767</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>45.650232617533</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>tis_total</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>ts_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>72.8352522620949</v>
+      </c>
+      <c r="C2">
+        <v>16.8081351374065</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>36.1644967968589</v>
+      </c>
+      <c r="C3">
+        <v>5.16635668526555</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>55.6151432089938</v>
+      </c>
+      <c r="C4">
+        <v>11.9175306876415</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>52.1702838063439</v>
+      </c>
+      <c r="C5">
+        <v>15.6510851419032</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>84.4322933419106</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>93.0095946739769</v>
+      </c>
+      <c r="C7">
+        <v>9.7904836498923</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>14.5751348199971</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>48.1395813030563</v>
+      </c>
+      <c r="C9">
+        <v>4.69654451737134</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>26.540452072367</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>91.1933298593017</v>
+      </c>
+      <c r="C11">
+        <v>26.0552371026576</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>90.0669068450849</v>
+      </c>
+      <c r="C12">
+        <v>38.6001029336078</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>96.8098838281394</v>
+      </c>
+      <c r="C13">
+        <v>13.8299834040199</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>132.710964671426</v>
+      </c>
+      <c r="C14">
+        <v>9.15248032216731</v>
       </c>
     </row>
   </sheetData>

--- a/03_Outputs/Bioenergetica_Norte/09_Salud/salud.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/09_Salud/salud.xlsx
@@ -880,7 +880,7 @@
     <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
     <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
     <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -916,7 +916,7 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>Tasa de leishmaniasis por 100 mil hab.</t>
+          <t>Tasa de leishmaniasis por 100 mil hab. rurales</t>
         </is>
       </c>
     </row>

--- a/03_Outputs/Bioenergetica_Norte/09_Salud/salud.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/09_Salud/salud.xlsx
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="E9" s="4">
-        <v>0.0886075949367088</v>
+        <v>0.0886075949367089</v>
       </c>
     </row>
     <row r="10">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="E15" s="7">
-        <v>8.23303539695201</v>
+        <v>8.23303539695202</v>
       </c>
       <c r="F15" s="9">
         <v>114.695337460052</v>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.0886075949367088</v>
+        <v>0.0886075949367089</v>
       </c>
     </row>
     <row r="10">
